--- a/app/reports/WAST_research.xlsx
+++ b/app/reports/WAST_research.xlsx
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-20 17:38 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-21 17:38 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>0.044509997</v>
+        <v>0.04450999999999999</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/WAST_research.xlsx
+++ b/app/reports/WAST_research.xlsx
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-21 17:38 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-22 17:39 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.036</v>
+        <v>0.0378</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>0.04450999999999999</v>
+        <v>0.04508999824523926</v>
       </c>
     </row>
     <row r="6">
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="B35" s="18" t="n">
-        <v>138036805.5555556</v>
+        <v>138036825.3968254</v>
       </c>
     </row>
     <row r="36">
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="B37" s="20" t="n">
-        <v>0.036</v>
+        <v>0.0378</v>
       </c>
     </row>
     <row r="38">
@@ -1481,7 +1481,7 @@
         </is>
       </c>
       <c r="C5" s="28" t="n">
-        <v>4969325</v>
+        <v>5217792</v>
       </c>
       <c r="D5" s="29" t="n"/>
       <c r="E5" s="29" t="n"/>

--- a/app/reports/WAST_research.xlsx
+++ b/app/reports/WAST_research.xlsx
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-22 17:39 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-23 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.0378</v>
+        <v>0.038</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>0.04508999824523926</v>
+        <v>0.04484999656677246</v>
       </c>
     </row>
     <row r="6">
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="B35" s="18" t="n">
-        <v>138036825.3968254</v>
+        <v>138036815.7894737</v>
       </c>
     </row>
     <row r="36">
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="B37" s="20" t="n">
-        <v>0.0378</v>
+        <v>0.038</v>
       </c>
     </row>
     <row r="38">
@@ -1481,12 +1481,12 @@
         </is>
       </c>
       <c r="C5" s="28" t="n">
-        <v>5217792</v>
+        <v>5245399</v>
       </c>
       <c r="D5" s="29" t="n"/>
       <c r="E5" s="29" t="n"/>
       <c r="F5" s="29" t="n">
-        <v>20.38</v>
+        <v>21.35</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/WAST_research.xlsx
+++ b/app/reports/WAST_research.xlsx
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-23 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-25 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.038</v>
+        <v>0.0367</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>0.04484999656677246</v>
+        <v>0.04383999824523926</v>
       </c>
     </row>
     <row r="6">
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="B35" s="18" t="n">
-        <v>138036815.7894737</v>
+        <v>138036811.9891008</v>
       </c>
     </row>
     <row r="36">
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="B37" s="20" t="n">
-        <v>0.038</v>
+        <v>0.0367</v>
       </c>
     </row>
     <row r="38">
@@ -1481,12 +1481,12 @@
         </is>
       </c>
       <c r="C5" s="28" t="n">
-        <v>5245399</v>
+        <v>5065951</v>
       </c>
       <c r="D5" s="29" t="n"/>
       <c r="E5" s="29" t="n"/>
       <c r="F5" s="29" t="n">
-        <v>21.35</v>
+        <v>18.26</v>
       </c>
     </row>
     <row r="6">
